--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/173.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/173.xlsx
@@ -426,13 +426,13 @@
         <v>-13.76440125298005</v>
       </c>
       <c r="E2">
-        <v>-11.01876201622925</v>
+        <v>-9.243174528665746</v>
       </c>
       <c r="F2">
-        <v>-0.8312361863629081</v>
+        <v>-0.729912770754681</v>
       </c>
       <c r="G2">
-        <v>-10.22163162608543</v>
+        <v>-13.85685891912064</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.8645661358826</v>
       </c>
       <c r="E3">
-        <v>-11.35177693780531</v>
+        <v>-10.85320100650882</v>
       </c>
       <c r="F3">
-        <v>-0.6841910319571622</v>
+        <v>-0.8254989137311187</v>
       </c>
       <c r="G3">
-        <v>-11.35731427333241</v>
+        <v>-14.46742283292843</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.84367235468122</v>
       </c>
       <c r="E4">
-        <v>-12.27581205907044</v>
+        <v>-11.27510987285545</v>
       </c>
       <c r="F4">
-        <v>-0.1708119908069742</v>
+        <v>-0.6195435831078832</v>
       </c>
       <c r="G4">
-        <v>-11.67506043419166</v>
+        <v>-14.38392425333693</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.68601139063857</v>
       </c>
       <c r="E5">
-        <v>-12.36195722011836</v>
+        <v>-11.77139439630406</v>
       </c>
       <c r="F5">
-        <v>-0.324566921175396</v>
+        <v>-0.3496034975576083</v>
       </c>
       <c r="G5">
-        <v>-10.91080113317767</v>
+        <v>-13.5804498851375</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.41774000988483</v>
       </c>
       <c r="E6">
-        <v>-14.35066827990485</v>
+        <v>-11.76792558521418</v>
       </c>
       <c r="F6">
-        <v>-0.3351252920914786</v>
+        <v>-0.0697992129747969</v>
       </c>
       <c r="G6">
-        <v>-10.50020410157849</v>
+        <v>-13.11854436349792</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.04733325714328</v>
       </c>
       <c r="E7">
-        <v>-14.35828517318575</v>
+        <v>-13.19807654699858</v>
       </c>
       <c r="F7">
-        <v>-0.5674840053115454</v>
+        <v>-0.06133495485299155</v>
       </c>
       <c r="G7">
-        <v>-10.09602621777995</v>
+        <v>-13.11097976694069</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.60445562462234</v>
       </c>
       <c r="E8">
-        <v>-15.33252295729992</v>
+        <v>-14.14885683575302</v>
       </c>
       <c r="F8">
-        <v>0.04351979099336988</v>
+        <v>0.008401154951684834</v>
       </c>
       <c r="G8">
-        <v>-10.62026103556015</v>
+        <v>-13.03991890694023</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.10995241265883</v>
       </c>
       <c r="E9">
-        <v>-15.81306650509787</v>
+        <v>-14.8364693860257</v>
       </c>
       <c r="F9">
-        <v>-0.4973718167059981</v>
+        <v>0.06034310457682503</v>
       </c>
       <c r="G9">
-        <v>-9.408664268552148</v>
+        <v>-12.71713740631575</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.57264580068164</v>
       </c>
       <c r="E10">
-        <v>-17.06953237479208</v>
+        <v>-16.08335753319369</v>
       </c>
       <c r="F10">
-        <v>-0.0518725140108128</v>
+        <v>-0.007795912875253899</v>
       </c>
       <c r="G10">
-        <v>-8.828597100252129</v>
+        <v>-11.84538469164162</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.01310237939849</v>
       </c>
       <c r="E11">
-        <v>-17.28953469903272</v>
+        <v>-17.46021741285582</v>
       </c>
       <c r="F11">
-        <v>0.2684082869749909</v>
+        <v>0.3890326630684465</v>
       </c>
       <c r="G11">
-        <v>-8.449019880355912</v>
+        <v>-11.07993690477904</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.44517382759612</v>
       </c>
       <c r="E12">
-        <v>-17.39931396592667</v>
+        <v>-17.40156008903447</v>
       </c>
       <c r="F12">
-        <v>0.1036476672929748</v>
+        <v>0.3537408982395763</v>
       </c>
       <c r="G12">
-        <v>-7.784427863347221</v>
+        <v>-10.43189430492116</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.871199653067746</v>
       </c>
       <c r="E13">
-        <v>-17.89008280803393</v>
+        <v>-17.72237077315986</v>
       </c>
       <c r="F13">
-        <v>0.6592560502704788</v>
+        <v>0.5931838094883847</v>
       </c>
       <c r="G13">
-        <v>-7.52410973595771</v>
+        <v>-10.33086969724476</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.31050295654739</v>
       </c>
       <c r="E14">
-        <v>-19.63437854020443</v>
+        <v>-18.92975251308493</v>
       </c>
       <c r="F14">
-        <v>0.3742082000279465</v>
+        <v>0.3983534530847465</v>
       </c>
       <c r="G14">
-        <v>-8.125569649532499</v>
+        <v>-8.450479830938731</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.773215435559491</v>
       </c>
       <c r="E15">
-        <v>-22.14059455263947</v>
+        <v>-18.88597575485278</v>
       </c>
       <c r="F15">
-        <v>0.8422763726124044</v>
+        <v>-0.1173516437325025</v>
       </c>
       <c r="G15">
-        <v>-5.891848568365591</v>
+        <v>-7.821472867931665</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.259540798572083</v>
       </c>
       <c r="E16">
-        <v>-21.20967615088268</v>
+        <v>-19.52699936453455</v>
       </c>
       <c r="F16">
-        <v>0.5165979296299591</v>
+        <v>0.2535573161776013</v>
       </c>
       <c r="G16">
-        <v>-5.004148955828796</v>
+        <v>-6.785960707611952</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.782287746563709</v>
       </c>
       <c r="E17">
-        <v>-20.80632949949349</v>
+        <v>-20.83550645752491</v>
       </c>
       <c r="F17">
-        <v>0.328898988197022</v>
+        <v>0.6913196673306392</v>
       </c>
       <c r="G17">
-        <v>-5.490597206823765</v>
+        <v>-6.677096728098559</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.342028623758519</v>
       </c>
       <c r="E18">
-        <v>-21.48122156627862</v>
+        <v>-21.99281233187316</v>
       </c>
       <c r="F18">
-        <v>0.455273062433309</v>
+        <v>0.4368410593536171</v>
       </c>
       <c r="G18">
-        <v>-4.685949250230667</v>
+        <v>-6.80895244638219</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.930798594390218</v>
       </c>
       <c r="E19">
-        <v>-23.59456981617823</v>
+        <v>-22.26915792971724</v>
       </c>
       <c r="F19">
-        <v>0.6836241341586319</v>
+        <v>0.09009971842018888</v>
       </c>
       <c r="G19">
-        <v>-3.731833473085015</v>
+        <v>-6.062450911640853</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.552900558884728</v>
       </c>
       <c r="E20">
-        <v>-24.71927520614526</v>
+        <v>-22.57617488201526</v>
       </c>
       <c r="F20">
-        <v>0.6361545401412062</v>
+        <v>0.7858546120729244</v>
       </c>
       <c r="G20">
-        <v>-4.053376829677807</v>
+        <v>-4.95589113350284</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.206277539354927</v>
       </c>
       <c r="E21">
-        <v>-25.517912353664</v>
+        <v>-23.9248767102977</v>
       </c>
       <c r="F21">
-        <v>0.9937052473137652</v>
+        <v>0.4946445367209666</v>
       </c>
       <c r="G21">
-        <v>-3.551279629918704</v>
+        <v>-4.665579463527532</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.88670220937643</v>
       </c>
       <c r="E22">
-        <v>-24.22752368517833</v>
+        <v>-23.02945248781303</v>
       </c>
       <c r="F22">
-        <v>1.376531929047945</v>
+        <v>0.7547958046723597</v>
       </c>
       <c r="G22">
-        <v>-1.623270876575793</v>
+        <v>-4.725033550867304</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.604415590929695</v>
       </c>
       <c r="E23">
-        <v>-26.81419256683364</v>
+        <v>-24.15915278461052</v>
       </c>
       <c r="F23">
-        <v>1.229740255067456</v>
+        <v>0.7925329100742941</v>
       </c>
       <c r="G23">
-        <v>-1.675997935379765</v>
+        <v>-3.07348514496339</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.368650283592276</v>
       </c>
       <c r="E24">
-        <v>-24.34549949002616</v>
+        <v>-24.77858463022372</v>
       </c>
       <c r="F24">
-        <v>1.18956443603168</v>
+        <v>0.5331694195229633</v>
       </c>
       <c r="G24">
-        <v>-2.337156916664232</v>
+        <v>-3.116287188240627</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.18594657195913</v>
       </c>
       <c r="E25">
-        <v>-26.09913293560047</v>
+        <v>-24.97585854341986</v>
       </c>
       <c r="F25">
-        <v>1.119618749274096</v>
+        <v>0.4951307883864099</v>
       </c>
       <c r="G25">
-        <v>-1.201950987974906</v>
+        <v>-3.413120632928299</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.067979673087195</v>
       </c>
       <c r="E26">
-        <v>-25.62355712378894</v>
+        <v>-25.08411171457322</v>
       </c>
       <c r="F26">
-        <v>1.054326830585439</v>
+        <v>0.5059078482968316</v>
       </c>
       <c r="G26">
-        <v>-2.489759823842476</v>
+        <v>-2.29192162241563</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.021466174382906</v>
       </c>
       <c r="E27">
-        <v>-25.56259480669768</v>
+        <v>-25.42423181186732</v>
       </c>
       <c r="F27">
-        <v>0.8693407923966698</v>
+        <v>0.4735733550959556</v>
       </c>
       <c r="G27">
-        <v>-1.460792612053902</v>
+        <v>-2.138308998847908</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.045798870432206</v>
       </c>
       <c r="E28">
-        <v>-25.87981441093499</v>
+        <v>-25.26471631494713</v>
       </c>
       <c r="F28">
-        <v>0.8534725864286424</v>
+        <v>0.5078843329199111</v>
       </c>
       <c r="G28">
-        <v>-1.51494982653084</v>
+        <v>-1.983570789796833</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.142672268569577</v>
       </c>
       <c r="E29">
-        <v>-25.63086608083732</v>
+        <v>-25.15533555376586</v>
       </c>
       <c r="F29">
-        <v>0.8853746718452571</v>
+        <v>0.852970595782546</v>
       </c>
       <c r="G29">
-        <v>-1.970249154546806</v>
+        <v>-2.213018080032641</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.312507428880717</v>
       </c>
       <c r="E30">
-        <v>-25.56200157660268</v>
+        <v>-23.87662129127197</v>
       </c>
       <c r="F30">
-        <v>1.082999939865941</v>
+        <v>0.1379785259345975</v>
       </c>
       <c r="G30">
-        <v>-1.270876546102532</v>
+        <v>-2.304091187817991</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.548403408957902</v>
       </c>
       <c r="E31">
-        <v>-25.49407446648762</v>
+        <v>-23.79850058616565</v>
       </c>
       <c r="F31">
-        <v>0.7703923061322688</v>
+        <v>0.2946136897625532</v>
       </c>
       <c r="G31">
-        <v>-1.209704285627879</v>
+        <v>-2.199974530607912</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.843841581298425</v>
       </c>
       <c r="E32">
-        <v>-25.27076635622138</v>
+        <v>-23.60638460486424</v>
       </c>
       <c r="F32">
-        <v>0.5686309996694073</v>
+        <v>0.1192276014048279</v>
       </c>
       <c r="G32">
-        <v>-0.7326381206912047</v>
+        <v>-2.086396334246596</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.191176898993896</v>
       </c>
       <c r="E33">
-        <v>-24.38855622089109</v>
+        <v>-23.20066050462102</v>
       </c>
       <c r="F33">
-        <v>1.129075391544455</v>
+        <v>0.2933396606970476</v>
       </c>
       <c r="G33">
-        <v>-2.026730371992312</v>
+        <v>-2.941156018667642</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.574490576203736</v>
       </c>
       <c r="E34">
-        <v>-23.0497445798414</v>
+        <v>-22.25301391987989</v>
       </c>
       <c r="F34">
-        <v>0.6254545183992449</v>
+        <v>-0.5426263562883379</v>
       </c>
       <c r="G34">
-        <v>-3.015444660568887</v>
+        <v>-2.836906939635992</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.977395397947439</v>
       </c>
       <c r="E35">
-        <v>-22.95078383735178</v>
+        <v>-22.0792110874655</v>
       </c>
       <c r="F35">
-        <v>0.7164573045359931</v>
+        <v>0.1525428816106184</v>
       </c>
       <c r="G35">
-        <v>-0.5325884748441254</v>
+        <v>-2.998180165581588</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.386629635590161</v>
       </c>
       <c r="E36">
-        <v>-22.96937775162727</v>
+        <v>-20.64214061739738</v>
       </c>
       <c r="F36">
-        <v>1.049021965737911</v>
+        <v>0.03018390417570063</v>
       </c>
       <c r="G36">
-        <v>-2.580243654521837</v>
+        <v>-3.61225656820654</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.782236623882191</v>
       </c>
       <c r="E37">
-        <v>-22.53390157715366</v>
+        <v>-20.81785899431702</v>
       </c>
       <c r="F37">
-        <v>0.5962636794919932</v>
+        <v>0.4356308145781271</v>
       </c>
       <c r="G37">
-        <v>-2.97600613155955</v>
+        <v>-4.133260293540421</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.149015234629886</v>
       </c>
       <c r="E38">
-        <v>-22.7782263352895</v>
+        <v>-20.52670981494187</v>
       </c>
       <c r="F38">
-        <v>1.384886842672581</v>
+        <v>0.01607680730602505</v>
       </c>
       <c r="G38">
-        <v>-3.014908352191525</v>
+        <v>-4.436241421294521</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.479255606927314</v>
       </c>
       <c r="E39">
-        <v>-20.2128820377363</v>
+        <v>-20.40638826055807</v>
       </c>
       <c r="F39">
-        <v>0.8158547659327113</v>
+        <v>0.1404147544662308</v>
       </c>
       <c r="G39">
-        <v>-2.621512915214391</v>
+        <v>-4.742053065484696</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.761048640810197</v>
       </c>
       <c r="E40">
-        <v>-20.25065403943428</v>
+        <v>-19.05316701521597</v>
       </c>
       <c r="F40">
-        <v>0.9809318219625968</v>
+        <v>0.2162227973334276</v>
       </c>
       <c r="G40">
-        <v>-3.754010817652593</v>
+        <v>-5.285777064854596</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.988592044739748</v>
       </c>
       <c r="E41">
-        <v>-19.96389295137256</v>
+        <v>-18.80613422962355</v>
       </c>
       <c r="F41">
-        <v>1.48221007209269</v>
+        <v>0.1724700878523633</v>
       </c>
       <c r="G41">
-        <v>-3.532647879623686</v>
+        <v>-5.873673673354991</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.161194884166024</v>
       </c>
       <c r="E42">
-        <v>-19.19550601022507</v>
+        <v>-16.88561745991856</v>
       </c>
       <c r="F42">
-        <v>1.506449759033409</v>
+        <v>0.4660062188713821</v>
       </c>
       <c r="G42">
-        <v>-4.500356756753585</v>
+        <v>-5.902260234086598</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.276499790561187</v>
       </c>
       <c r="E43">
-        <v>-18.76622025971994</v>
+        <v>-16.93390910673636</v>
       </c>
       <c r="F43">
-        <v>1.387603887753764</v>
+        <v>0.958454900855035</v>
       </c>
       <c r="G43">
-        <v>-4.872544839006149</v>
+        <v>-6.278732162266978</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.338896194899986</v>
       </c>
       <c r="E44">
-        <v>-18.28097615590203</v>
+        <v>-16.38757136008097</v>
       </c>
       <c r="F44">
-        <v>1.515715876801124</v>
+        <v>0.4578393446471818</v>
       </c>
       <c r="G44">
-        <v>-6.23043792394009</v>
+        <v>-7.160466171742005</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.3555360991739</v>
       </c>
       <c r="E45">
-        <v>-16.49373237624279</v>
+        <v>-14.91509728022088</v>
       </c>
       <c r="F45">
-        <v>1.582256973533203</v>
+        <v>0.9624045566315831</v>
       </c>
       <c r="G45">
-        <v>-6.030252545725901</v>
+        <v>-6.879582935462541</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.329840689408032</v>
       </c>
       <c r="E46">
-        <v>-15.12612416897832</v>
+        <v>-14.59895998127141</v>
       </c>
       <c r="F46">
-        <v>1.349192491285951</v>
+        <v>0.7510830619730123</v>
       </c>
       <c r="G46">
-        <v>-6.969033875933649</v>
+        <v>-7.606764126436693</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.269874400209043</v>
       </c>
       <c r="E47">
-        <v>-15.85273140893105</v>
+        <v>-14.13631296275177</v>
       </c>
       <c r="F47">
-        <v>1.296664057539628</v>
+        <v>0.6073944522834102</v>
       </c>
       <c r="G47">
-        <v>-6.331601574529139</v>
+        <v>-8.255011980118002</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.181538065005983</v>
       </c>
       <c r="E48">
-        <v>-15.11671399999038</v>
+        <v>-13.6112952717245</v>
       </c>
       <c r="F48">
-        <v>1.398593009719302</v>
+        <v>1.16778334354247</v>
       </c>
       <c r="G48">
-        <v>-7.145373394628468</v>
+        <v>-8.97448953162227</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.0670231575436</v>
       </c>
       <c r="E49">
-        <v>-14.05089235754509</v>
+        <v>-13.18139364875432</v>
       </c>
       <c r="F49">
-        <v>1.854158633093307</v>
+        <v>1.186201264376314</v>
       </c>
       <c r="G49">
-        <v>-7.141433845436735</v>
+        <v>-8.594167438979717</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.931829380425562</v>
       </c>
       <c r="E50">
-        <v>-13.65140396601043</v>
+        <v>-11.9385539573492</v>
       </c>
       <c r="F50">
-        <v>1.684139537138319</v>
+        <v>0.9522322049252051</v>
       </c>
       <c r="G50">
-        <v>-7.717640917637964</v>
+        <v>-9.307709182332072</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.776599165753986</v>
       </c>
       <c r="E51">
-        <v>-13.11446280292096</v>
+        <v>-12.09097333549937</v>
       </c>
       <c r="F51">
-        <v>1.238454680144907</v>
+        <v>1.076248745533125</v>
       </c>
       <c r="G51">
-        <v>-8.838184440133858</v>
+        <v>-9.77966717550165</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.599884173854386</v>
       </c>
       <c r="E52">
-        <v>-12.78267962627498</v>
+        <v>-11.1226452099652</v>
       </c>
       <c r="F52">
-        <v>1.664555275001334</v>
+        <v>1.060647273868799</v>
       </c>
       <c r="G52">
-        <v>-9.508440800560241</v>
+        <v>-10.22180046390794</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.403576124576315</v>
       </c>
       <c r="E53">
-        <v>-11.57904293435425</v>
+        <v>-10.69940044378631</v>
       </c>
       <c r="F53">
-        <v>1.779251025592953</v>
+        <v>1.14622425351721</v>
       </c>
       <c r="G53">
-        <v>-8.283416460844949</v>
+        <v>-11.28280713542558</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.183574001299487</v>
       </c>
       <c r="E54">
-        <v>-11.86341298813992</v>
+        <v>-9.772267846299927</v>
       </c>
       <c r="F54">
-        <v>1.787773269432954</v>
+        <v>1.049154504522358</v>
       </c>
       <c r="G54">
-        <v>-8.448993395991598</v>
+        <v>-11.44804639492722</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.936551173011527</v>
       </c>
       <c r="E55">
-        <v>-11.53222757006296</v>
+        <v>-9.787492575913713</v>
       </c>
       <c r="F55">
-        <v>1.87654112031695</v>
+        <v>0.9117283523979205</v>
       </c>
       <c r="G55">
-        <v>-8.263516771608391</v>
+        <v>-10.07275970372995</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.662526454344347</v>
       </c>
       <c r="E56">
-        <v>-10.8724379640934</v>
+        <v>-9.779078671207463</v>
       </c>
       <c r="F56">
-        <v>1.482544732523421</v>
+        <v>0.9421244658762455</v>
       </c>
       <c r="G56">
-        <v>-8.781868749965316</v>
+        <v>-11.60082476101905</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.354472439580154</v>
       </c>
       <c r="E57">
-        <v>-10.82529654967355</v>
+        <v>-8.687245474062109</v>
       </c>
       <c r="F57">
-        <v>2.178628488035068</v>
+        <v>1.297233974312754</v>
       </c>
       <c r="G57">
-        <v>-8.838035465584591</v>
+        <v>-11.6633708978925</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.008962848589148</v>
       </c>
       <c r="E58">
-        <v>-9.697529911277336</v>
+        <v>-8.034343677058219</v>
       </c>
       <c r="F58">
-        <v>1.586874293436407</v>
+        <v>1.028564604358374</v>
       </c>
       <c r="G58">
-        <v>-9.48391958975086</v>
+        <v>-11.35407655979501</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.626049246450044</v>
       </c>
       <c r="E59">
-        <v>-10.81360402978575</v>
+        <v>-9.038229380500608</v>
       </c>
       <c r="F59">
-        <v>1.66189124543393</v>
+        <v>0.7549498810092805</v>
       </c>
       <c r="G59">
-        <v>-9.010733384186212</v>
+        <v>-11.14600877265181</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.200031562767588</v>
       </c>
       <c r="E60">
-        <v>-8.362282179271684</v>
+        <v>-8.284514695137961</v>
       </c>
       <c r="F60">
-        <v>1.279639450677293</v>
+        <v>0.722295637990924</v>
       </c>
       <c r="G60">
-        <v>-8.241842629962781</v>
+        <v>-10.45896132525024</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.732545392879408</v>
       </c>
       <c r="E61">
-        <v>-11.02347162919722</v>
+        <v>-8.734835207408716</v>
       </c>
       <c r="F61">
-        <v>1.167607729653077</v>
+        <v>0.6331218870795572</v>
       </c>
       <c r="G61">
-        <v>-10.45573023280392</v>
+        <v>-11.60876675976776</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.227820870622705</v>
       </c>
       <c r="E62">
-        <v>-7.113043754093717</v>
+        <v>-7.707170486952052</v>
       </c>
       <c r="F62">
-        <v>1.528363390307067</v>
+        <v>0.7936412656592398</v>
       </c>
       <c r="G62">
-        <v>-8.851539180839277</v>
+        <v>-11.44394462900406</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.683236027905812</v>
       </c>
       <c r="E63">
-        <v>-9.056488187699534</v>
+        <v>-8.427424277872023</v>
       </c>
       <c r="F63">
-        <v>0.8881298218269682</v>
+        <v>0.6774958721127211</v>
       </c>
       <c r="G63">
-        <v>-9.451688118380515</v>
+        <v>-11.50494143056513</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.105399283262875</v>
       </c>
       <c r="E64">
-        <v>-8.685796362379655</v>
+        <v>-6.719428793347009</v>
       </c>
       <c r="F64">
-        <v>1.458480659472095</v>
+        <v>0.1494017124192027</v>
       </c>
       <c r="G64">
-        <v>-9.203271402204685</v>
+        <v>-11.24286540349427</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.500299577460645</v>
       </c>
       <c r="E65">
-        <v>-10.27328462508655</v>
+        <v>-7.064140763284884</v>
       </c>
       <c r="F65">
-        <v>0.8206907748302549</v>
+        <v>0.4555505655132467</v>
       </c>
       <c r="G65">
-        <v>-7.944002779431171</v>
+        <v>-10.93817603424191</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.867486747945275</v>
       </c>
       <c r="E66">
-        <v>-7.466423223282272</v>
+        <v>-7.535867372189897</v>
       </c>
       <c r="F66">
-        <v>1.061169145332562</v>
+        <v>0.4306722073049692</v>
       </c>
       <c r="G66">
-        <v>-8.590777440347503</v>
+        <v>-9.977541792929429</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.218104984971907</v>
       </c>
       <c r="E67">
-        <v>-9.787234452895277</v>
+        <v>-6.41622481616344</v>
       </c>
       <c r="F67">
-        <v>0.8211894520067401</v>
+        <v>0.2043788002082003</v>
       </c>
       <c r="G67">
-        <v>-8.096059446595435</v>
+        <v>-11.16301504508705</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.55769724003054</v>
       </c>
       <c r="E68">
-        <v>-8.130338269072816</v>
+        <v>-7.382225306057657</v>
       </c>
       <c r="F68">
-        <v>0.2546822391106031</v>
+        <v>0.1860917614239984</v>
       </c>
       <c r="G68">
-        <v>-8.640097947791567</v>
+        <v>-9.773777714987288</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.8849755759463396</v>
       </c>
       <c r="E69">
-        <v>-8.202925178941765</v>
+        <v>-7.368590070820562</v>
       </c>
       <c r="F69">
-        <v>0.6353924421306306</v>
+        <v>0.1666350678670436</v>
       </c>
       <c r="G69">
-        <v>-7.107947677307007</v>
+        <v>-10.31803140164347</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.2085660346778393</v>
       </c>
       <c r="E70">
-        <v>-8.274447897418909</v>
+        <v>-6.899897539500688</v>
       </c>
       <c r="F70">
-        <v>0.2006436915889773</v>
+        <v>-0.1974365475003531</v>
       </c>
       <c r="G70">
-        <v>-8.405982788345387</v>
+        <v>-10.109139288661</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.468793906172828</v>
       </c>
       <c r="E71">
-        <v>-9.599275610732912</v>
+        <v>-6.049712772352639</v>
       </c>
       <c r="F71">
-        <v>0.985863921478865</v>
+        <v>-0.2914363669004298</v>
       </c>
       <c r="G71">
-        <v>-7.02081080816785</v>
+        <v>-9.441528054120493</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.150871447344377</v>
       </c>
       <c r="E72">
-        <v>-9.723265229062926</v>
+        <v>-8.232917262294565</v>
       </c>
       <c r="F72">
-        <v>0.5958304433403291</v>
+        <v>-0.3502098624964575</v>
       </c>
       <c r="G72">
-        <v>-6.920620457967347</v>
+        <v>-8.834330965126146</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.828986936160516</v>
       </c>
       <c r="E73">
-        <v>-10.33534736136167</v>
+        <v>-8.271776097754385</v>
       </c>
       <c r="F73">
-        <v>0.4898499461935631</v>
+        <v>-0.318266358709703</v>
       </c>
       <c r="G73">
-        <v>-7.334683630746151</v>
+        <v>-8.788191891945324</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.501626838976964</v>
       </c>
       <c r="E74">
-        <v>-8.327480856522737</v>
+        <v>-8.572724894882134</v>
       </c>
       <c r="F74">
-        <v>0.2134378261252157</v>
+        <v>-0.2786952478779706</v>
       </c>
       <c r="G74">
-        <v>-5.398239607369177</v>
+        <v>-8.249536337796048</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.170854167766617</v>
       </c>
       <c r="E75">
-        <v>-9.347601139282624</v>
+        <v>-8.482544863493386</v>
       </c>
       <c r="F75">
-        <v>0.4507261537593424</v>
+        <v>-0.03824835533696933</v>
       </c>
       <c r="G75">
-        <v>-5.425554918613704</v>
+        <v>-7.895576119282712</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.825338765342765</v>
       </c>
       <c r="E76">
-        <v>-10.31804859065237</v>
+        <v>-9.407277369755704</v>
       </c>
       <c r="F76">
-        <v>0.2304326117610503</v>
+        <v>-0.4144199333570584</v>
       </c>
       <c r="G76">
-        <v>-5.801106515134167</v>
+        <v>-7.149968431836976</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>4.462512588620217</v>
       </c>
       <c r="E77">
-        <v>-8.874135596358665</v>
+        <v>-9.13617574481251</v>
       </c>
       <c r="F77">
-        <v>0.212833117921172</v>
+        <v>-0.4809709704979707</v>
       </c>
       <c r="G77">
-        <v>-4.689094268492975</v>
+        <v>-6.394174195766904</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>5.082334247415702</v>
       </c>
       <c r="E78">
-        <v>-11.58315026027921</v>
+        <v>-11.00596002020956</v>
       </c>
       <c r="F78">
-        <v>0.1549956774903077</v>
+        <v>-0.8308476820509951</v>
       </c>
       <c r="G78">
-        <v>-3.803304840732341</v>
+        <v>-6.746879717520856</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>5.67303834452443</v>
       </c>
       <c r="E79">
-        <v>-11.25974928902143</v>
+        <v>-11.10179158715988</v>
       </c>
       <c r="F79">
-        <v>0.2591206316548028</v>
+        <v>-1.195857009318361</v>
       </c>
       <c r="G79">
-        <v>-3.549339650232691</v>
+        <v>-6.377965764806632</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>6.233964619901782</v>
       </c>
       <c r="E80">
-        <v>-12.19392819206375</v>
+        <v>-10.99234742734251</v>
       </c>
       <c r="F80">
-        <v>0.02402416416848351</v>
+        <v>-0.4443148845566898</v>
       </c>
       <c r="G80">
-        <v>-2.840392944088845</v>
+        <v>-4.925861174916111</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>6.765788226966224</v>
       </c>
       <c r="E81">
-        <v>-13.01242269810612</v>
+        <v>-12.33811933294198</v>
       </c>
       <c r="F81">
-        <v>0.03371606278123773</v>
+        <v>-0.967117433281125</v>
       </c>
       <c r="G81">
-        <v>-1.983468162885116</v>
+        <v>-4.127347659207283</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>7.257972812720625</v>
       </c>
       <c r="E82">
-        <v>-14.5312955226488</v>
+        <v>-13.30945889369124</v>
       </c>
       <c r="F82">
-        <v>-0.4665151309517165</v>
+        <v>-0.4310709465207313</v>
       </c>
       <c r="G82">
-        <v>-1.960728025575862</v>
+        <v>-4.003255170213242</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>7.711457566763973</v>
       </c>
       <c r="E83">
-        <v>-15.9677682341479</v>
+        <v>-14.85219224778033</v>
       </c>
       <c r="F83">
-        <v>-0.5930333411160906</v>
+        <v>-1.112765960245751</v>
       </c>
       <c r="G83">
-        <v>-1.285035749373995</v>
+        <v>-2.562164765331876</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>8.125730853859416</v>
       </c>
       <c r="E84">
-        <v>-15.30844958947515</v>
+        <v>-15.3394198232136</v>
       </c>
       <c r="F84">
-        <v>-0.0009154932276012059</v>
+        <v>-0.8832104423167574</v>
       </c>
       <c r="G84">
-        <v>-0.896357839790322</v>
+        <v>-1.591271143393198</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>8.491516094401272</v>
       </c>
       <c r="E85">
-        <v>-18.11186029408558</v>
+        <v>-16.15682296702013</v>
       </c>
       <c r="F85">
-        <v>-0.778372263818452</v>
+        <v>-1.082407123300552</v>
       </c>
       <c r="G85">
-        <v>-0.09179595738124539</v>
+        <v>-1.799130366167418</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>8.808541412769456</v>
       </c>
       <c r="E86">
-        <v>-18.5338778438084</v>
+        <v>-18.44660962120658</v>
       </c>
       <c r="F86">
-        <v>-0.6870928029691689</v>
+        <v>-1.180071640090613</v>
       </c>
       <c r="G86">
-        <v>0.02936007771946225</v>
+        <v>-1.065801492126839</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>9.071995636127863</v>
       </c>
       <c r="E87">
-        <v>-21.02679825655692</v>
+        <v>-18.81717012078024</v>
       </c>
       <c r="F87">
-        <v>-0.7956387539624049</v>
+        <v>-1.063607325094017</v>
       </c>
       <c r="G87">
-        <v>-0.4317525682634643</v>
+        <v>-0.7449003813686652</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>9.271837955927381</v>
       </c>
       <c r="E88">
-        <v>-19.24494788944081</v>
+        <v>-20.33423155571985</v>
       </c>
       <c r="F88">
-        <v>-0.5510309719571417</v>
+        <v>-1.203888859655905</v>
       </c>
       <c r="G88">
-        <v>0.6132376839351822</v>
+        <v>-0.2746870456982821</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>9.405833140247163</v>
       </c>
       <c r="E89">
-        <v>-22.57304117800195</v>
+        <v>-20.68181910665259</v>
       </c>
       <c r="F89">
-        <v>-1.359564774031419</v>
+        <v>-1.238727507515444</v>
       </c>
       <c r="G89">
-        <v>0.03359095491865082</v>
+        <v>-0.7342205614589763</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>9.465180737922974</v>
       </c>
       <c r="E90">
-        <v>-25.08359094006234</v>
+        <v>-22.5446702883439</v>
       </c>
       <c r="F90">
-        <v>-1.083964454017815</v>
+        <v>-1.482953412148016</v>
       </c>
       <c r="G90">
-        <v>0.6639916575977488</v>
+        <v>0.1641886658973599</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>9.4426410931987</v>
       </c>
       <c r="E91">
-        <v>-26.1398258030334</v>
+        <v>-24.32394848222365</v>
       </c>
       <c r="F91">
-        <v>-1.664352619482663</v>
+        <v>-1.544213666687248</v>
       </c>
       <c r="G91">
-        <v>1.831511821295901</v>
+        <v>-0.3634758770615353</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>9.336273219912714</v>
       </c>
       <c r="E92">
-        <v>-27.25294735648881</v>
+        <v>-26.88950561805521</v>
       </c>
       <c r="F92">
-        <v>-1.572779088205386</v>
+        <v>-1.818024713110805</v>
       </c>
       <c r="G92">
-        <v>0.7882827793241463</v>
+        <v>0.4380734089068045</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>9.138705477317249</v>
       </c>
       <c r="E93">
-        <v>-28.09237699786864</v>
+        <v>-28.01019425157744</v>
       </c>
       <c r="F93">
-        <v>-1.411046151380603</v>
+        <v>-1.70554650205648</v>
       </c>
       <c r="G93">
-        <v>0.5426105054003707</v>
+        <v>-0.1641313774143208</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>8.848970401225307</v>
       </c>
       <c r="E94">
-        <v>-29.90418322054549</v>
+        <v>-29.68314161152009</v>
       </c>
       <c r="F94">
-        <v>-1.360397283271232</v>
+        <v>-1.652542585420951</v>
       </c>
       <c r="G94">
-        <v>0.7334038659196478</v>
+        <v>0.4469887080440618</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>8.473439904354256</v>
       </c>
       <c r="E95">
-        <v>-32.93075259577991</v>
+        <v>-32.17096522677298</v>
       </c>
       <c r="F95">
-        <v>-1.748330850043672</v>
+        <v>-1.776252630089834</v>
       </c>
       <c r="G95">
-        <v>1.320062330388356</v>
+        <v>-0.1971739324417865</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>8.005095343113807</v>
       </c>
       <c r="E96">
-        <v>-34.12293677693524</v>
+        <v>-33.15718535311144</v>
       </c>
       <c r="F96">
-        <v>-2.487889811956445</v>
+        <v>-2.200098408875841</v>
       </c>
       <c r="G96">
-        <v>0.2781508855412312</v>
+        <v>0.2046931905703429</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>7.464298553702562</v>
       </c>
       <c r="E97">
-        <v>-35.48224881981766</v>
+        <v>-36.29482008185799</v>
       </c>
       <c r="F97">
-        <v>-2.336301890713746</v>
+        <v>-2.08275105422786</v>
       </c>
       <c r="G97">
-        <v>-0.6702873060045712</v>
+        <v>-0.7214319240407717</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>6.842750899588474</v>
       </c>
       <c r="E98">
-        <v>-38.74338862017539</v>
+        <v>-37.98918712385692</v>
       </c>
       <c r="F98">
-        <v>-2.519371086732437</v>
+        <v>-2.331745041630946</v>
       </c>
       <c r="G98">
-        <v>0.6077487994310706</v>
+        <v>-0.5322176937437271</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>6.178462538545371</v>
       </c>
       <c r="E99">
-        <v>-38.25021062989605</v>
+        <v>-40.12066059097222</v>
       </c>
       <c r="F99">
-        <v>-3.207628427022434</v>
+        <v>-2.593019575780536</v>
       </c>
       <c r="G99">
-        <v>-0.6843173980000025</v>
+        <v>-0.8696913954714925</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>5.437380135932968</v>
       </c>
       <c r="E100">
-        <v>-41.77512272001556</v>
+        <v>-43.47137813567569</v>
       </c>
       <c r="F100">
-        <v>-3.042253987094944</v>
+        <v>-2.734187463463419</v>
       </c>
       <c r="G100">
-        <v>-0.6354967829323702</v>
+        <v>-1.797991538501908</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.712583979131542</v>
       </c>
       <c r="E101">
-        <v>-44.62749075712292</v>
+        <v>-44.13860349596584</v>
       </c>
       <c r="F101">
-        <v>-3.091030744873987</v>
+        <v>-2.713827849437413</v>
       </c>
       <c r="G101">
-        <v>0.005011015278122664</v>
+        <v>-1.795399381344659</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.87714811411734</v>
       </c>
       <c r="E102">
-        <v>-45.52139567657802</v>
+        <v>-46.17790666736602</v>
       </c>
       <c r="F102">
-        <v>-3.328720002331069</v>
+        <v>-3.123873855660182</v>
       </c>
       <c r="G102">
-        <v>-1.975946603419892</v>
+        <v>-2.002811680471078</v>
       </c>
     </row>
   </sheetData>
